--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BP18"/>
+  <dimension ref="A2:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,9 @@
     <col width="9" customWidth="1" min="66" max="66"/>
     <col width="9" customWidth="1" min="67" max="67"/>
     <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -634,8 +637,11 @@
       <c r="BK3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BN3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="BQ3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -967,17 +973,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BN4" s="6" t="inlineStr">
+      <c r="BN4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BO4" s="6" t="inlineStr">
+      <c r="BO4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BP4" s="6" t="inlineStr">
+      <c r="BP4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BQ4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BR4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BS4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1104,15 +1125,26 @@
         <f>BL5/$D$5</f>
         <v/>
       </c>
-      <c r="BN5" s="12">
+      <c r="BN5" s="10">
         <f>BO5-BL5</f>
         <v/>
       </c>
-      <c r="BO5" s="12" t="n">
+      <c r="BO5" s="10" t="n">
         <v>214</v>
       </c>
-      <c r="BP5" s="13">
+      <c r="BP5" s="11">
         <f>BO5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BQ5" s="12">
+        <f>BR5-BO5</f>
+        <v/>
+      </c>
+      <c r="BR5" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="BS5" s="13">
+        <f>BR5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1357,15 +1389,26 @@
         <f>BL6/$D$6</f>
         <v/>
       </c>
-      <c r="BN6" s="12">
+      <c r="BN6" s="10">
         <f>BO6-BL6</f>
         <v/>
       </c>
-      <c r="BO6" s="12" t="n">
+      <c r="BO6" s="10" t="n">
         <v>392</v>
       </c>
-      <c r="BP6" s="13">
+      <c r="BP6" s="11">
         <f>BO6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BQ6" s="12">
+        <f>BR6-BO6</f>
+        <v/>
+      </c>
+      <c r="BR6" s="12" t="n">
+        <v>402</v>
+      </c>
+      <c r="BS6" s="13">
+        <f>BR6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1453,9 +1496,12 @@
       <c r="BK7" s="10" t="n"/>
       <c r="BL7" s="10" t="n"/>
       <c r="BM7" s="11" t="n"/>
-      <c r="BN7" s="12" t="n"/>
-      <c r="BO7" s="12" t="n"/>
-      <c r="BP7" s="13" t="n"/>
+      <c r="BN7" s="10" t="n"/>
+      <c r="BO7" s="10" t="n"/>
+      <c r="BP7" s="11" t="n"/>
+      <c r="BQ7" s="12" t="n"/>
+      <c r="BR7" s="12" t="n"/>
+      <c r="BS7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1698,15 +1744,26 @@
         <f>BL8/$D$8</f>
         <v/>
       </c>
-      <c r="BN8" s="12">
+      <c r="BN8" s="10">
         <f>BO8-BL8</f>
         <v/>
       </c>
-      <c r="BO8" s="12" t="n">
+      <c r="BO8" s="10" t="n">
         <v>1028</v>
       </c>
-      <c r="BP8" s="13">
+      <c r="BP8" s="11">
         <f>BO8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BQ8" s="12">
+        <f>BR8-BO8</f>
+        <v/>
+      </c>
+      <c r="BR8" s="12" t="n">
+        <v>1039</v>
+      </c>
+      <c r="BS8" s="13">
+        <f>BR8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -1951,15 +2008,26 @@
         <f>BL9/$D$9</f>
         <v/>
       </c>
-      <c r="BN9" s="12">
+      <c r="BN9" s="10">
         <f>BO9-BL9</f>
         <v/>
       </c>
-      <c r="BO9" s="12" t="n">
+      <c r="BO9" s="10" t="n">
         <v>1132</v>
       </c>
-      <c r="BP9" s="13">
+      <c r="BP9" s="11">
         <f>BO9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BQ9" s="12">
+        <f>BR9-BO9</f>
+        <v/>
+      </c>
+      <c r="BR9" s="12" t="n">
+        <v>1132</v>
+      </c>
+      <c r="BS9" s="13">
+        <f>BR9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2204,15 +2272,26 @@
         <f>BL10/$D$10</f>
         <v/>
       </c>
-      <c r="BN10" s="12">
+      <c r="BN10" s="10">
         <f>BO10-BL10</f>
         <v/>
       </c>
-      <c r="BO10" s="12" t="n">
+      <c r="BO10" s="10" t="n">
         <v>530</v>
       </c>
-      <c r="BP10" s="13">
+      <c r="BP10" s="11">
         <f>BO10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BQ10" s="12">
+        <f>BR10-BO10</f>
+        <v/>
+      </c>
+      <c r="BR10" s="12" t="n">
+        <v>535</v>
+      </c>
+      <c r="BS10" s="13">
+        <f>BR10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2457,15 +2536,26 @@
         <f>BL11/$D$11</f>
         <v/>
       </c>
-      <c r="BN11" s="12">
+      <c r="BN11" s="10">
         <f>BO11-BL11</f>
         <v/>
       </c>
-      <c r="BO11" s="12" t="n">
+      <c r="BO11" s="10" t="n">
         <v>470</v>
       </c>
-      <c r="BP11" s="13">
+      <c r="BP11" s="11">
         <f>BO11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BQ11" s="12">
+        <f>BR11-BO11</f>
+        <v/>
+      </c>
+      <c r="BR11" s="12" t="n">
+        <v>470</v>
+      </c>
+      <c r="BS11" s="13">
+        <f>BR11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2710,15 +2800,26 @@
         <f>BL12/$D$12</f>
         <v/>
       </c>
-      <c r="BN12" s="12">
+      <c r="BN12" s="10">
         <f>BO12-BL12</f>
         <v/>
       </c>
-      <c r="BO12" s="12" t="n">
+      <c r="BO12" s="10" t="n">
         <v>238</v>
       </c>
-      <c r="BP12" s="13">
+      <c r="BP12" s="11">
         <f>BO12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BQ12" s="12">
+        <f>BR12-BO12</f>
+        <v/>
+      </c>
+      <c r="BR12" s="12" t="n">
+        <v>239</v>
+      </c>
+      <c r="BS12" s="13">
+        <f>BR12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -2963,15 +3064,26 @@
         <f>BL13/$D$13</f>
         <v/>
       </c>
-      <c r="BN13" s="12">
+      <c r="BN13" s="10">
         <f>BO13-BL13</f>
         <v/>
       </c>
-      <c r="BO13" s="12" t="n">
+      <c r="BO13" s="10" t="n">
         <v>677</v>
       </c>
-      <c r="BP13" s="13">
+      <c r="BP13" s="11">
         <f>BO13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BQ13" s="12">
+        <f>BR13-BO13</f>
+        <v/>
+      </c>
+      <c r="BR13" s="12" t="n">
+        <v>684</v>
+      </c>
+      <c r="BS13" s="13">
+        <f>BR13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -3216,15 +3328,26 @@
         <f>BL14/$D$14</f>
         <v/>
       </c>
-      <c r="BN14" s="12">
+      <c r="BN14" s="10">
         <f>BO14-BL14</f>
         <v/>
       </c>
-      <c r="BO14" s="12" t="n">
+      <c r="BO14" s="10" t="n">
         <v>1173</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BP14" s="11">
         <f>BO14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BQ14" s="12">
+        <f>BR14-BO14</f>
+        <v/>
+      </c>
+      <c r="BR14" s="12" t="n">
+        <v>1179</v>
+      </c>
+      <c r="BS14" s="13">
+        <f>BR14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3469,15 +3592,26 @@
         <f>BL15/$D$15</f>
         <v/>
       </c>
-      <c r="BN15" s="12">
+      <c r="BN15" s="10">
         <f>BO15-BL15</f>
         <v/>
       </c>
-      <c r="BO15" s="12" t="n">
+      <c r="BO15" s="10" t="n">
         <v>149</v>
       </c>
-      <c r="BP15" s="13">
+      <c r="BP15" s="11">
         <f>BO15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BQ15" s="12">
+        <f>BR15-BO15</f>
+        <v/>
+      </c>
+      <c r="BR15" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="BS15" s="13">
+        <f>BR15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3658,15 +3792,26 @@
         <f>BL16/$D$16</f>
         <v/>
       </c>
-      <c r="BN16" s="12">
+      <c r="BN16" s="10">
         <f>BO16-BL16</f>
         <v/>
       </c>
-      <c r="BO16" s="12" t="n">
+      <c r="BO16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BP16" s="11">
         <f>BO16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BQ16" s="12">
+        <f>BR16-BO16</f>
+        <v/>
+      </c>
+      <c r="BR16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BS16" s="13">
+        <f>BR16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3748,9 +3893,12 @@
       <c r="BK17" s="10" t="n"/>
       <c r="BL17" s="10" t="n"/>
       <c r="BM17" s="11" t="n"/>
-      <c r="BN17" s="12" t="n"/>
-      <c r="BO17" s="12" t="n"/>
-      <c r="BP17" s="13" t="n"/>
+      <c r="BN17" s="10" t="n"/>
+      <c r="BO17" s="10" t="n"/>
+      <c r="BP17" s="11" t="n"/>
+      <c r="BQ17" s="12" t="n"/>
+      <c r="BR17" s="12" t="n"/>
+      <c r="BS17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3873,26 +4021,38 @@
         <f>BL18/$D$18</f>
         <v/>
       </c>
-      <c r="BN18" s="12">
+      <c r="BN18" s="10">
         <f>BO18-BL18</f>
         <v/>
       </c>
-      <c r="BO18" s="12" t="n">
+      <c r="BO18" s="10" t="n">
         <v>402</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BP18" s="11">
         <f>BO18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BQ18" s="12">
+        <f>BR18-BO18</f>
+        <v/>
+      </c>
+      <c r="BR18" s="12" t="n">
+        <v>440</v>
+      </c>
+      <c r="BS18" s="13">
+        <f>BR18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BS18"/>
+  <dimension ref="A2:BV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,9 @@
     <col width="9" customWidth="1" min="69" max="69"/>
     <col width="9" customWidth="1" min="70" max="70"/>
     <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -640,8 +643,11 @@
       <c r="BN3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BQ3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="BT3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -988,17 +994,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BQ4" s="6" t="inlineStr">
+      <c r="BQ4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BR4" s="6" t="inlineStr">
+      <c r="BR4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BS4" s="6" t="inlineStr">
+      <c r="BS4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BU4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BV4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1136,15 +1157,26 @@
         <f>BO5/$D$5</f>
         <v/>
       </c>
-      <c r="BQ5" s="12">
+      <c r="BQ5" s="10">
         <f>BR5-BO5</f>
         <v/>
       </c>
-      <c r="BR5" s="12" t="n">
+      <c r="BR5" s="10" t="n">
         <v>229</v>
       </c>
-      <c r="BS5" s="13">
+      <c r="BS5" s="11">
         <f>BR5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BT5" s="12">
+        <f>BU5-BR5</f>
+        <v/>
+      </c>
+      <c r="BU5" s="12" t="n">
+        <v>245</v>
+      </c>
+      <c r="BV5" s="13">
+        <f>BU5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1400,15 +1432,26 @@
         <f>BO6/$D$6</f>
         <v/>
       </c>
-      <c r="BQ6" s="12">
+      <c r="BQ6" s="10">
         <f>BR6-BO6</f>
         <v/>
       </c>
-      <c r="BR6" s="12" t="n">
+      <c r="BR6" s="10" t="n">
         <v>402</v>
       </c>
-      <c r="BS6" s="13">
+      <c r="BS6" s="11">
         <f>BR6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BT6" s="12">
+        <f>BU6-BR6</f>
+        <v/>
+      </c>
+      <c r="BU6" s="12" t="n">
+        <v>416</v>
+      </c>
+      <c r="BV6" s="13">
+        <f>BU6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1499,9 +1542,12 @@
       <c r="BN7" s="10" t="n"/>
       <c r="BO7" s="10" t="n"/>
       <c r="BP7" s="11" t="n"/>
-      <c r="BQ7" s="12" t="n"/>
-      <c r="BR7" s="12" t="n"/>
-      <c r="BS7" s="13" t="n"/>
+      <c r="BQ7" s="10" t="n"/>
+      <c r="BR7" s="10" t="n"/>
+      <c r="BS7" s="11" t="n"/>
+      <c r="BT7" s="12" t="n"/>
+      <c r="BU7" s="12" t="n"/>
+      <c r="BV7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1755,15 +1801,26 @@
         <f>BO8/$D$8</f>
         <v/>
       </c>
-      <c r="BQ8" s="12">
+      <c r="BQ8" s="10">
         <f>BR8-BO8</f>
         <v/>
       </c>
-      <c r="BR8" s="12" t="n">
+      <c r="BR8" s="10" t="n">
         <v>1039</v>
       </c>
-      <c r="BS8" s="13">
+      <c r="BS8" s="11">
         <f>BR8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BT8" s="12">
+        <f>BU8-BR8</f>
+        <v/>
+      </c>
+      <c r="BU8" s="12" t="n">
+        <v>1046</v>
+      </c>
+      <c r="BV8" s="13">
+        <f>BU8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -2019,15 +2076,26 @@
         <f>BO9/$D$9</f>
         <v/>
       </c>
-      <c r="BQ9" s="12">
+      <c r="BQ9" s="10">
         <f>BR9-BO9</f>
         <v/>
       </c>
-      <c r="BR9" s="12" t="n">
+      <c r="BR9" s="10" t="n">
         <v>1132</v>
       </c>
-      <c r="BS9" s="13">
+      <c r="BS9" s="11">
         <f>BR9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BT9" s="12">
+        <f>BU9-BR9</f>
+        <v/>
+      </c>
+      <c r="BU9" s="12" t="n">
+        <v>1130</v>
+      </c>
+      <c r="BV9" s="13">
+        <f>BU9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2283,15 +2351,26 @@
         <f>BO10/$D$10</f>
         <v/>
       </c>
-      <c r="BQ10" s="12">
+      <c r="BQ10" s="10">
         <f>BR10-BO10</f>
         <v/>
       </c>
-      <c r="BR10" s="12" t="n">
+      <c r="BR10" s="10" t="n">
         <v>535</v>
       </c>
-      <c r="BS10" s="13">
+      <c r="BS10" s="11">
         <f>BR10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BT10" s="12">
+        <f>BU10-BR10</f>
+        <v/>
+      </c>
+      <c r="BU10" s="12" t="n">
+        <v>552</v>
+      </c>
+      <c r="BV10" s="13">
+        <f>BU10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2547,15 +2626,26 @@
         <f>BO11/$D$11</f>
         <v/>
       </c>
-      <c r="BQ11" s="12">
+      <c r="BQ11" s="10">
         <f>BR11-BO11</f>
         <v/>
       </c>
-      <c r="BR11" s="12" t="n">
+      <c r="BR11" s="10" t="n">
         <v>470</v>
       </c>
-      <c r="BS11" s="13">
+      <c r="BS11" s="11">
         <f>BR11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BT11" s="12">
+        <f>BU11-BR11</f>
+        <v/>
+      </c>
+      <c r="BU11" s="12" t="n">
+        <v>470</v>
+      </c>
+      <c r="BV11" s="13">
+        <f>BU11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2811,15 +2901,26 @@
         <f>BO12/$D$12</f>
         <v/>
       </c>
-      <c r="BQ12" s="12">
+      <c r="BQ12" s="10">
         <f>BR12-BO12</f>
         <v/>
       </c>
-      <c r="BR12" s="12" t="n">
+      <c r="BR12" s="10" t="n">
         <v>239</v>
       </c>
-      <c r="BS12" s="13">
+      <c r="BS12" s="11">
         <f>BR12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BT12" s="12">
+        <f>BU12-BR12</f>
+        <v/>
+      </c>
+      <c r="BU12" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="BV12" s="13">
+        <f>BU12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -3075,15 +3176,26 @@
         <f>BO13/$D$13</f>
         <v/>
       </c>
-      <c r="BQ13" s="12">
+      <c r="BQ13" s="10">
         <f>BR13-BO13</f>
         <v/>
       </c>
-      <c r="BR13" s="12" t="n">
+      <c r="BR13" s="10" t="n">
         <v>684</v>
       </c>
-      <c r="BS13" s="13">
+      <c r="BS13" s="11">
         <f>BR13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BT13" s="12">
+        <f>BU13-BR13</f>
+        <v/>
+      </c>
+      <c r="BU13" s="12" t="n">
+        <v>697</v>
+      </c>
+      <c r="BV13" s="13">
+        <f>BU13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -3339,15 +3451,26 @@
         <f>BO14/$D$14</f>
         <v/>
       </c>
-      <c r="BQ14" s="12">
+      <c r="BQ14" s="10">
         <f>BR14-BO14</f>
         <v/>
       </c>
-      <c r="BR14" s="12" t="n">
+      <c r="BR14" s="10" t="n">
         <v>1179</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BS14" s="11">
         <f>BR14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BT14" s="12">
+        <f>BU14-BR14</f>
+        <v/>
+      </c>
+      <c r="BU14" s="12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="BV14" s="13">
+        <f>BU14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3603,15 +3726,26 @@
         <f>BO15/$D$15</f>
         <v/>
       </c>
-      <c r="BQ15" s="12">
+      <c r="BQ15" s="10">
         <f>BR15-BO15</f>
         <v/>
       </c>
-      <c r="BR15" s="12" t="n">
+      <c r="BR15" s="10" t="n">
         <v>153</v>
       </c>
-      <c r="BS15" s="13">
+      <c r="BS15" s="11">
         <f>BR15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BT15" s="12">
+        <f>BU15-BR15</f>
+        <v/>
+      </c>
+      <c r="BU15" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="BV15" s="13">
+        <f>BU15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3803,15 +3937,26 @@
         <f>BO16/$D$16</f>
         <v/>
       </c>
-      <c r="BQ16" s="12">
+      <c r="BQ16" s="10">
         <f>BR16-BO16</f>
         <v/>
       </c>
-      <c r="BR16" s="12" t="n">
+      <c r="BR16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BS16" s="11">
         <f>BR16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BT16" s="12">
+        <f>BU16-BR16</f>
+        <v/>
+      </c>
+      <c r="BU16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BV16" s="13">
+        <f>BU16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3896,9 +4041,12 @@
       <c r="BN17" s="10" t="n"/>
       <c r="BO17" s="10" t="n"/>
       <c r="BP17" s="11" t="n"/>
-      <c r="BQ17" s="12" t="n"/>
-      <c r="BR17" s="12" t="n"/>
-      <c r="BS17" s="13" t="n"/>
+      <c r="BQ17" s="10" t="n"/>
+      <c r="BR17" s="10" t="n"/>
+      <c r="BS17" s="11" t="n"/>
+      <c r="BT17" s="12" t="n"/>
+      <c r="BU17" s="12" t="n"/>
+      <c r="BV17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -4032,25 +4180,37 @@
         <f>BO18/$D$18</f>
         <v/>
       </c>
-      <c r="BQ18" s="12">
+      <c r="BQ18" s="10">
         <f>BR18-BO18</f>
         <v/>
       </c>
-      <c r="BR18" s="12" t="n">
+      <c r="BR18" s="10" t="n">
         <v>440</v>
       </c>
-      <c r="BS18" s="13">
+      <c r="BS18" s="11">
         <f>BR18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BT18" s="12">
+        <f>BU18-BR18</f>
+        <v/>
+      </c>
+      <c r="BU18" s="12" t="n">
+        <v>465</v>
+      </c>
+      <c r="BV18" s="13">
+        <f>BU18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BV18"/>
+  <dimension ref="A2:BY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -565,6 +565,9 @@
     <col width="9" customWidth="1" min="72" max="72"/>
     <col width="9" customWidth="1" min="73" max="73"/>
     <col width="9" customWidth="1" min="74" max="74"/>
+    <col width="9" customWidth="1" min="75" max="75"/>
+    <col width="9" customWidth="1" min="76" max="76"/>
+    <col width="9" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -646,8 +649,11 @@
       <c r="BQ3" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BT3" s="3" t="n">
         <v>46297</v>
+      </c>
+      <c r="BW3" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -1009,17 +1015,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BT4" s="6" t="inlineStr">
+      <c r="BT4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BU4" s="6" t="inlineStr">
+      <c r="BU4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BV4" s="6" t="inlineStr">
+      <c r="BV4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BW4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BX4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BY4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1168,15 +1189,26 @@
         <f>BR5/$D$5</f>
         <v/>
       </c>
-      <c r="BT5" s="12">
+      <c r="BT5" s="10">
         <f>BU5-BR5</f>
         <v/>
       </c>
-      <c r="BU5" s="12" t="n">
+      <c r="BU5" s="10" t="n">
         <v>245</v>
       </c>
-      <c r="BV5" s="13">
+      <c r="BV5" s="11">
         <f>BU5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BW5" s="12">
+        <f>BX5-BU5</f>
+        <v/>
+      </c>
+      <c r="BX5" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="BY5" s="13">
+        <f>BX5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1443,15 +1475,26 @@
         <f>BR6/$D$6</f>
         <v/>
       </c>
-      <c r="BT6" s="12">
+      <c r="BT6" s="10">
         <f>BU6-BR6</f>
         <v/>
       </c>
-      <c r="BU6" s="12" t="n">
+      <c r="BU6" s="10" t="n">
         <v>416</v>
       </c>
-      <c r="BV6" s="13">
+      <c r="BV6" s="11">
         <f>BU6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BW6" s="12">
+        <f>BX6-BU6</f>
+        <v/>
+      </c>
+      <c r="BX6" s="12" t="n">
+        <v>423</v>
+      </c>
+      <c r="BY6" s="13">
+        <f>BX6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1545,9 +1588,12 @@
       <c r="BQ7" s="10" t="n"/>
       <c r="BR7" s="10" t="n"/>
       <c r="BS7" s="11" t="n"/>
-      <c r="BT7" s="12" t="n"/>
-      <c r="BU7" s="12" t="n"/>
-      <c r="BV7" s="13" t="n"/>
+      <c r="BT7" s="10" t="n"/>
+      <c r="BU7" s="10" t="n"/>
+      <c r="BV7" s="11" t="n"/>
+      <c r="BW7" s="12" t="n"/>
+      <c r="BX7" s="12" t="n"/>
+      <c r="BY7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1812,15 +1858,26 @@
         <f>BR8/$D$8</f>
         <v/>
       </c>
-      <c r="BT8" s="12">
+      <c r="BT8" s="10">
         <f>BU8-BR8</f>
         <v/>
       </c>
-      <c r="BU8" s="12" t="n">
+      <c r="BU8" s="10" t="n">
         <v>1046</v>
       </c>
-      <c r="BV8" s="13">
+      <c r="BV8" s="11">
         <f>BU8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BW8" s="12">
+        <f>BX8-BU8</f>
+        <v/>
+      </c>
+      <c r="BX8" s="12" t="n">
+        <v>1052</v>
+      </c>
+      <c r="BY8" s="13">
+        <f>BX8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -2087,15 +2144,26 @@
         <f>BR9/$D$9</f>
         <v/>
       </c>
-      <c r="BT9" s="12">
+      <c r="BT9" s="10">
         <f>BU9-BR9</f>
         <v/>
       </c>
-      <c r="BU9" s="12" t="n">
+      <c r="BU9" s="10" t="n">
         <v>1130</v>
       </c>
-      <c r="BV9" s="13">
+      <c r="BV9" s="11">
         <f>BU9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BW9" s="12">
+        <f>BX9-BU9</f>
+        <v/>
+      </c>
+      <c r="BX9" s="12" t="n">
+        <v>1132</v>
+      </c>
+      <c r="BY9" s="13">
+        <f>BX9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2362,15 +2430,26 @@
         <f>BR10/$D$10</f>
         <v/>
       </c>
-      <c r="BT10" s="12">
+      <c r="BT10" s="10">
         <f>BU10-BR10</f>
         <v/>
       </c>
-      <c r="BU10" s="12" t="n">
+      <c r="BU10" s="10" t="n">
         <v>552</v>
       </c>
-      <c r="BV10" s="13">
+      <c r="BV10" s="11">
         <f>BU10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BW10" s="12">
+        <f>BX10-BU10</f>
+        <v/>
+      </c>
+      <c r="BX10" s="12" t="n">
+        <v>565</v>
+      </c>
+      <c r="BY10" s="13">
+        <f>BX10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2637,15 +2716,26 @@
         <f>BR11/$D$11</f>
         <v/>
       </c>
-      <c r="BT11" s="12">
+      <c r="BT11" s="10">
         <f>BU11-BR11</f>
         <v/>
       </c>
-      <c r="BU11" s="12" t="n">
+      <c r="BU11" s="10" t="n">
         <v>470</v>
       </c>
-      <c r="BV11" s="13">
+      <c r="BV11" s="11">
         <f>BU11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BW11" s="12">
+        <f>BX11-BU11</f>
+        <v/>
+      </c>
+      <c r="BX11" s="12" t="n">
+        <v>471</v>
+      </c>
+      <c r="BY11" s="13">
+        <f>BX11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2912,15 +3002,26 @@
         <f>BR12/$D$12</f>
         <v/>
       </c>
-      <c r="BT12" s="12">
+      <c r="BT12" s="10">
         <f>BU12-BR12</f>
         <v/>
       </c>
-      <c r="BU12" s="12" t="n">
+      <c r="BU12" s="10" t="n">
         <v>240</v>
       </c>
-      <c r="BV12" s="13">
+      <c r="BV12" s="11">
         <f>BU12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BW12" s="12">
+        <f>BX12-BU12</f>
+        <v/>
+      </c>
+      <c r="BX12" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="BY12" s="13">
+        <f>BX12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -3187,15 +3288,26 @@
         <f>BR13/$D$13</f>
         <v/>
       </c>
-      <c r="BT13" s="12">
+      <c r="BT13" s="10">
         <f>BU13-BR13</f>
         <v/>
       </c>
-      <c r="BU13" s="12" t="n">
+      <c r="BU13" s="10" t="n">
         <v>697</v>
       </c>
-      <c r="BV13" s="13">
+      <c r="BV13" s="11">
         <f>BU13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BW13" s="12">
+        <f>BX13-BU13</f>
+        <v/>
+      </c>
+      <c r="BX13" s="12" t="n">
+        <v>711</v>
+      </c>
+      <c r="BY13" s="13">
+        <f>BX13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -3462,15 +3574,26 @@
         <f>BR14/$D$14</f>
         <v/>
       </c>
-      <c r="BT14" s="12">
+      <c r="BT14" s="10">
         <f>BU14-BR14</f>
         <v/>
       </c>
-      <c r="BU14" s="12" t="n">
+      <c r="BU14" s="10" t="n">
         <v>1186</v>
       </c>
-      <c r="BV14" s="13">
+      <c r="BV14" s="11">
         <f>BU14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BW14" s="12">
+        <f>BX14-BU14</f>
+        <v/>
+      </c>
+      <c r="BX14" s="12" t="n">
+        <v>1189</v>
+      </c>
+      <c r="BY14" s="13">
+        <f>BX14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3737,15 +3860,26 @@
         <f>BR15/$D$15</f>
         <v/>
       </c>
-      <c r="BT15" s="12">
+      <c r="BT15" s="10">
         <f>BU15-BR15</f>
         <v/>
       </c>
-      <c r="BU15" s="12" t="n">
+      <c r="BU15" s="10" t="n">
         <v>156</v>
       </c>
-      <c r="BV15" s="13">
+      <c r="BV15" s="11">
         <f>BU15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BW15" s="12">
+        <f>BX15-BU15</f>
+        <v/>
+      </c>
+      <c r="BX15" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="BY15" s="13">
+        <f>BX15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3948,15 +4082,26 @@
         <f>BR16/$D$16</f>
         <v/>
       </c>
-      <c r="BT16" s="12">
+      <c r="BT16" s="10">
         <f>BU16-BR16</f>
         <v/>
       </c>
-      <c r="BU16" s="12" t="n">
+      <c r="BU16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BV16" s="13">
+      <c r="BV16" s="11">
         <f>BU16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BW16" s="12">
+        <f>BX16-BU16</f>
+        <v/>
+      </c>
+      <c r="BX16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BY16" s="13">
+        <f>BX16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -4044,9 +4189,12 @@
       <c r="BQ17" s="10" t="n"/>
       <c r="BR17" s="10" t="n"/>
       <c r="BS17" s="11" t="n"/>
-      <c r="BT17" s="12" t="n"/>
-      <c r="BU17" s="12" t="n"/>
-      <c r="BV17" s="13" t="n"/>
+      <c r="BT17" s="10" t="n"/>
+      <c r="BU17" s="10" t="n"/>
+      <c r="BV17" s="11" t="n"/>
+      <c r="BW17" s="12" t="n"/>
+      <c r="BX17" s="12" t="n"/>
+      <c r="BY17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -4191,20 +4339,31 @@
         <f>BR18/$D$18</f>
         <v/>
       </c>
-      <c r="BT18" s="12">
+      <c r="BT18" s="10">
         <f>BU18-BR18</f>
         <v/>
       </c>
-      <c r="BU18" s="12" t="n">
+      <c r="BU18" s="10" t="n">
         <v>465</v>
       </c>
-      <c r="BV18" s="13">
+      <c r="BV18" s="11">
         <f>BU18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BW18" s="12">
+        <f>BX18-BU18</f>
+        <v/>
+      </c>
+      <c r="BX18" s="12" t="n">
+        <v>492</v>
+      </c>
+      <c r="BY18" s="13">
+        <f>BX18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
@@ -4214,6 +4373,7 @@
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
+    <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="G3:H3"/>
